--- a/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="92">
   <si>
     <t>SCGLY</t>
   </si>
@@ -656,149 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,86 +844,89 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3">
         <v>19131600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3">
         <v>14651300</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3">
         <v>11756000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3">
         <v>10311300</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="3">
         <v>9862300</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3">
         <v>11817800</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD8" s="3">
         <v>13838500</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="3">
         <v>13949800</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3">
         <v>13909700</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>11989100</v>
       </c>
-      <c r="AJ8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL8" s="3">
         <v>12963500</v>
       </c>
-      <c r="AL8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM8" s="3">
+      <c r="AM8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN8" s="3">
         <v>13604100</v>
       </c>
-      <c r="AN8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO8" s="3">
+      <c r="AO8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP8" s="3">
         <v>14341600</v>
       </c>
-      <c r="AP8" s="3" t="s">
+      <c r="AQ8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1041,8 +1047,11 @@
       <c r="AP9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,8 +1592,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1617,86 +1639,89 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>-885000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3">
         <v>-837800</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3">
         <v>-921500</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15" s="3">
         <v>-841100</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-854800</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-814900</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-889600</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-852900</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-611600</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-534700</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="3">
         <v>-589000</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-539700</v>
       </c>
-      <c r="AN15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO15" s="3">
+      <c r="AO15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP15" s="3">
         <v>-567000</v>
       </c>
-      <c r="AP15" s="3" t="s">
+      <c r="AQ15" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,8 +1761,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1780,86 +1806,89 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3">
         <v>12803900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>492800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8687400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>608700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5863900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>211100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5462500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>292000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6073200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>537600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8143600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>925900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8100700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>403000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8077200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>315800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8066200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>292400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5419700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>228400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8273600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>574500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8121000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>736000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>10070100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1902,86 +1931,89 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>6327700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>5963900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V18" s="3">
         <v>5892100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X18" s="3">
         <v>4848800</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z18" s="3">
         <v>3789100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3674200</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>5737800</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>5872600</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>5843500</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>6569300</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL18" s="3">
         <v>4689900</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN18" s="3">
         <v>5483200</v>
       </c>
-      <c r="AN18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO18" s="3">
+      <c r="AO18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP18" s="3">
         <v>4271500</v>
       </c>
-      <c r="AP18" s="3" t="s">
+      <c r="AQ18" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,86 +2101,89 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>-2102200</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>-5502500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V20" s="3">
         <v>-703600</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1411400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1628800</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-4509800</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-2833300</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-2670400</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-2423800</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-3027200</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-2053200</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-2355100</v>
       </c>
-      <c r="AN20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO20" s="3">
+      <c r="AO20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP20" s="3">
         <v>-1122200</v>
       </c>
-      <c r="AP20" s="3" t="s">
+      <c r="AQ20" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2190,86 +2226,89 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>10142300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>11090300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3">
         <v>7409700</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>5908300</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>6270200</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>6188900</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>6010500</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>5141000</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN21" s="3">
         <v>5429300</v>
       </c>
-      <c r="AN21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP21" s="3">
         <v>5489900</v>
       </c>
-      <c r="AP21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,8 +2429,11 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2434,86 +2476,89 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3">
         <v>4225500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2236000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>461400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1468000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5188500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2671800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3437400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1301300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2160400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1514300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-835600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-275500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2904500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1749300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3202200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1312200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3419800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2149900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3542100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1508700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2636700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1742500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3128100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1500100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3149300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1962600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2556,86 +2601,89 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3">
         <v>911600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>398800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>718100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>361300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1094900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>752800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>726800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>299400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>590500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>484700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>667600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-51900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>722600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>476500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>758800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>305000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>637600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>597000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>840000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>406300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1141100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>515000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>775300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>456600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1124500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>528200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,8 +2804,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2800,86 +2851,89 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3">
         <v>3313900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1837200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-256800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1106700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4093600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1919000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2710600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1001900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1569900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1029600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1503300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-223600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2181900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1272800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2443400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1007200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2782200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1552900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2702200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1102400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1495600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1227500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2352800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1043500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2024800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2922,86 +2976,89 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3">
         <v>2433400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1426500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1053300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>763800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3368300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1584100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2056800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>708900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1038300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>762900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-547600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1346000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>825600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1627000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>623200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1915100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1239400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1957700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>821300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>885300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>939100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1740200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>727800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1452000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3166,8 +3226,8 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,86 +3601,89 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>2102200</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>5502500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V32" s="3">
         <v>703600</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X32" s="3">
         <v>1411400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1628800</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="3">
         <v>4509800</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>2833300</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>2670400</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>2423800</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>3027200</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL32" s="3">
         <v>2053200</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN32" s="3">
         <v>2355100</v>
       </c>
-      <c r="AN32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO32" s="3">
+      <c r="AO32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP32" s="3">
         <v>1122200</v>
       </c>
-      <c r="AP32" s="3" t="s">
+      <c r="AQ32" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3654,86 +3726,89 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3">
         <v>2433400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1426500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1053300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>763800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3368300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1584100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2056800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>708900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1038300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>762900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-547600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1346000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>825600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1627000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>623200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1915100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1239400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1957700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>821300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>885300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>939100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1740200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>727800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1452000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,8 +3929,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3898,213 +3976,219 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3">
         <v>2433400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1426500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1053300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>763800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3368300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1584100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2056800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>708900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1038300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>762900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-547600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1346000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>825600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1627000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>623200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1915100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1239400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1957700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>821300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>885300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>939100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1740200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>727800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1452000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>203886700</v>
+      </c>
+      <c r="E41" s="3">
         <v>178238200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>209342500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>192419300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>226473300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>183626200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>254869000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>222105700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>285282300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>234898000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>290533900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>247675700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>280915900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>242447800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>360815100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>301050600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>259139700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>330465000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>244721500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>261336700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>217609400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>254792900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>209707300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>225571000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>202919100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>220891500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>163996600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>194104600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171349700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>197168400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>164605300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>178050000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>144180600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>171178200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>170037600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>183782000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>179666500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>204477700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>167576600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>177127900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>615069100</v>
+      </c>
+      <c r="E42" s="3">
         <v>699131800</v>
       </c>
-      <c r="E42" s="3">
-        <v>530510700</v>
-      </c>
       <c r="F42" s="3">
+        <v>545902300</v>
+      </c>
+      <c r="G42" s="3">
         <v>710691100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>584486200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>601696900</v>
       </c>
-      <c r="I42" s="3">
-        <v>435670400</v>
-      </c>
       <c r="J42" s="3">
+        <v>456868200</v>
+      </c>
+      <c r="K42" s="3">
         <v>598030300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>490460700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>582460900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>454422500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>550563100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>498040400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>568965700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>568974100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>55417200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>494726400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>36272600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>427770700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>35223200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>530635700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>34644200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>467173200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>38143900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>525051700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>37311100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>529056200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>42058800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>579304100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>31521100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>513271000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>25238900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>488778000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>25473600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>484036600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>16268900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>595802500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>19015700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>651761500</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>27115000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20382700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4972900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20861800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4764800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>17832100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>103433900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15679700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5058000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18892100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>94427700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16369000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97063900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16064400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4796800</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>111845100</v>
+      </c>
+      <c r="E45" s="3">
         <v>3120000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>96528100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3465900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>66637700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3146300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>108953300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44546100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>91860100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30835000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>82510200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1684000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>81909400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1140800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>953673000</v>
+      </c>
+      <c r="E46" s="3">
         <v>885462900</v>
       </c>
-      <c r="E46" s="3">
-        <v>859424700</v>
-      </c>
       <c r="F46" s="3">
+        <v>874816200</v>
+      </c>
+      <c r="G46" s="3">
         <v>911341100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>897805000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>891903400</v>
       </c>
-      <c r="I46" s="3">
-        <v>817027600</v>
-      </c>
       <c r="J46" s="3">
+        <v>838225500</v>
+      </c>
+      <c r="K46" s="3">
         <v>869740100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>888550300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>942621600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>843835500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>896986700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>878956300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>817351200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>344609800</v>
+      </c>
+      <c r="E47" s="3">
         <v>183879900</v>
       </c>
-      <c r="E47" s="3">
-        <v>342381100</v>
-      </c>
       <c r="F47" s="3">
+        <v>326989600</v>
+      </c>
+      <c r="G47" s="3">
         <v>182785400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>322517900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>152276300</v>
       </c>
-      <c r="I47" s="3">
-        <v>278598200</v>
-      </c>
       <c r="J47" s="3">
+        <v>257400400</v>
+      </c>
+      <c r="K47" s="3">
         <v>138397300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>259011000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>127583300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>256665200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>124050600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>242974900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>131510200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>161700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>124300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>120800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>124800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>103000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>102300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>101600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>109000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>99700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>103800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>115600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>129800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>130700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>317300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>285900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>311000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>294500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>737700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>719200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>768600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>785400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>897600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>817900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1408600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1286500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1408600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>64147100</v>
+      </c>
+      <c r="E48" s="3">
         <v>69184800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>66524600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>70582000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66257200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66201900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>59330200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>68001300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>61329700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65732000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62352200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>62453400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>62811100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37437000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37611900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35715000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35488400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34870800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>34656500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33577700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>32571600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>32128300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>30009800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>30711500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32522200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>34099900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>33024900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>36724000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31480500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>34927800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31643800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>28864100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>28039600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27120600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>52821000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>26030200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>25510700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>26176000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>23553700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>24767400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9515600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6036000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9687700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5965000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9893100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5496100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8778300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5611200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9068900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5336100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9407500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5553600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6029500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4111300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4187800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4100200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4128300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4056800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4055600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4114800</v>
-      </c>
-      <c r="W49" s="3">
-        <v>4042600</v>
       </c>
       <c r="X49" s="3">
         <v>4042600</v>
       </c>
       <c r="Y49" s="3">
+        <v>4042600</v>
+      </c>
+      <c r="Z49" s="3">
         <v>4033500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4199300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4412700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5337300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8160200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5747700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8087800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5457100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5502900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5385200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5351700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5490000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7786600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5497800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5452900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5282100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7338700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5399500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16611400</v>
+      </c>
+      <c r="E52" s="3">
         <v>97901500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11957300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>88335100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12400500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>80158900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7712000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>84721200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9631400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>79254500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6109200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>87563500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8104800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>74657800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10223100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4869600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4209900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5059400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4181400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5058200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4621300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5898400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4095300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8964300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8922600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10436300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10796200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12949400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16134300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>20145200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>22854800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11710700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10751600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6807600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>7068500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>6956300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7286200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>12677100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>12528100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>8334100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1911906800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1875887200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1815945800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1873436600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1822068100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1680056200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1629097200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1761752200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1705929500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1716000600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1717746200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1692894800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1723176900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1687987800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1644675200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1722139800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1674176800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1745984200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1587609200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1643730600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1579180300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1590155000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1440648500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1528138600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1585498000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1702350800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1583361700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1728623800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1633559600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1631191000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1548922400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1444169700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1425228200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1396546200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1429639700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1502008000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1514935600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1644742600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1589834100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1649085700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,192 +6116,196 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>722564800</v>
+      </c>
+      <c r="E57" s="3">
         <v>621238300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>715560600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>620336700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>693417500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>563273900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>635552300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>586772300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>670938600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>572820200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>712377600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>575697500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>713595000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>582603200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24631900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3">
         <v>23345000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X57" s="3">
         <v>21322900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z57" s="3">
         <v>19225900</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="3">
         <v>22898200</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD57" s="3">
         <v>25886100</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="3">
         <v>30259400</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH57" s="3">
         <v>26338500</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>24286700</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL57" s="3">
         <v>22786500</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN57" s="3">
         <v>37729200</v>
       </c>
-      <c r="AN57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO57" s="3">
+      <c r="AO57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP57" s="3">
         <v>25001000</v>
       </c>
-      <c r="AP57" s="3" t="s">
+      <c r="AQ57" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>209851500</v>
+      </c>
+      <c r="E58" s="3">
         <v>22627700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>232464500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20646500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>180716400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20018400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>216699500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21950700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>141919000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>23454500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>209366600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>464061200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>385420300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48867900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>76110900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V58" s="3">
         <v>121369300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -6231,175 +6364,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>233625000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6670100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11947900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5823100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>236277200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5254000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34103900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>36045100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>238126000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22035800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>228724400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4253800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3342800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2184900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2890800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3">
         <v>2985600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
         <v>3007900</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3">
         <v>2016700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1815300</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD59" s="3">
         <v>2759800</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="3">
         <v>2592800</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH59" s="3">
         <v>2834200</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>2290400</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL59" s="3">
         <v>2852100</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN59" s="3">
         <v>2472900</v>
       </c>
-      <c r="AN59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP59" s="3">
         <v>3005000</v>
       </c>
-      <c r="AP59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1173024100</v>
+      </c>
+      <c r="E60" s="3">
         <v>650536100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>966609100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>646806300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1117048700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>588546300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>891436000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>644768000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1058070300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>618310500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1156958100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1044012500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1108622300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>633656000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>194870300</v>
+      </c>
+      <c r="E61" s="3">
         <v>321565800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123166600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>319669100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200932500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>293265200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>118668600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>317089000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>191327500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>318936200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>125073500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>304189200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>182185600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>308690800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>45062700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>154313200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>41412000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>164361200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>56119500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>160479600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53062900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>173731000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>54638600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>166334900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>59718600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>187453200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>61859900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>177461900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>43963200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>168898700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>54097600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>140870100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>41046500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>129673800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>41008700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>126560500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>41101900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>138392200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>41775900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>129706000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>446248100</v>
+      </c>
+      <c r="E62" s="3">
         <v>811124200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>627177400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>813720500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>407579600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>711705600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>531665800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>713747500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>369303500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>694836600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>345750000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>261863900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>341551300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>663752700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12209100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7178000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7097700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7302100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6968600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6783400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5772400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6505600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5943500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6783700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7107300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6967700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8322500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12323400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>15154400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17011200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19181900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12837100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11585000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>9003600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>8863700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>8078300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>7775400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>13029300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>12610200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>9507900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1819882300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1783226100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1722571300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1780195900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1731098100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1593517100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1546699500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1675604500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1624056600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1632083300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1633467400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1610065600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1638041500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1606099500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1570499300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1650477500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1603905100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1674534800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1517070000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1575198900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1512382400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1523585600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1379099000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1465249100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1519324500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1631690600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1509199600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1650573600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1560044000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1557229900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1476734700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1377548700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1360491200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1331874000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1364084000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1434352000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1447491600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1571731600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1517113000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1577600600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>50188500</v>
+      </c>
+      <c r="E72" s="3">
         <v>49834000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>49153500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47804800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>46743400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>42662100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>39406800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>41528000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>38572800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38705400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>39111300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>38585900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39577500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40320500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>78399300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38343200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>37034600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>40266500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>39322500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>37390000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35140400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34342700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31761200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>32832900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33673100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36431500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>38298100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>39706800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>37388300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>39071500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>38096500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>35056600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>33541700</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL72" s="3">
         <v>34225200</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN72" s="3">
         <v>33549700</v>
       </c>
-      <c r="AN72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP72" s="3">
         <v>34846900</v>
       </c>
-      <c r="AP72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>81851900</v>
+      </c>
+      <c r="E76" s="3">
         <v>81859800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>82357600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>81926600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>80203200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>76260300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>72736300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>75224200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71605100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>72652900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>72924700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>72054400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>74243400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>74692500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>74176000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>71662300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70271700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>71449400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>70539100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>68531800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>66797900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>66569400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>61549600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>62889500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>66173500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>70660200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>74162100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>78050200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>73515600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>73961000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>72187700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>66621000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>64737000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>64672200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>65555600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>67656000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>67443900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>73011000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>72721100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>71485000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,135 +8659,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8642,86 +8836,89 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3">
         <v>2433400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1426500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1053300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>763800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3368300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1584100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2056800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>708900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1038300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>762900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2083600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-547600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1346000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>825600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1627000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>623200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1915100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1239400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1957700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>821300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>885300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>939100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1740200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>727800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1452000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1152700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,86 +9006,89 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>5935600</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
         <v>5901800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
         <v>5249300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD83" s="3">
         <v>3003700</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF83" s="3">
         <v>3068100</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2769200</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>2468300</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL83" s="3">
         <v>2504300</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN83" s="3">
         <v>2301200</v>
       </c>
-      <c r="AN83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO83" s="3">
+      <c r="AO83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP83" s="3">
         <v>2340600</v>
       </c>
-      <c r="AP83" s="3" t="s">
+      <c r="AQ83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,8 +9709,11 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9540,86 +9756,89 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>43298300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3">
         <v>22772600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z89" s="3">
         <v>80580900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD89" s="3">
         <v>8778900</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF89" s="3">
         <v>3392700</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH89" s="3">
         <v>21205800</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-20841100</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL89" s="3">
         <v>9214900</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN89" s="3">
         <v>22647400</v>
       </c>
-      <c r="AN89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP89" s="3">
         <v>-13181900</v>
       </c>
-      <c r="AP89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,86 +9926,89 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3440000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-3566000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-2022000</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-5573500</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-4625300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-3820900</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-4820300</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-3893500</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-4770700</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-1880500</v>
       </c>
-      <c r="AN91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO91" s="3">
+      <c r="AO91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-4015600</v>
       </c>
-      <c r="AP91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,8 +10254,11 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10072,86 +10301,89 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R94" s="3">
         <v>-9969500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3">
         <v>-10838800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-6845200</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-5084100</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-3083300</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-5791500</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-9314300</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-4494700</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-2470600</v>
       </c>
-      <c r="AN94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-3732700</v>
       </c>
-      <c r="AP94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10281,11 +10514,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1036400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -10293,11 +10526,11 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1936900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
@@ -10305,19 +10538,22 @@
         <v>0</v>
       </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-1976900</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
         <v>0</v>
       </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,8 +10924,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10726,86 +10971,89 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R100" s="3">
         <v>-237000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3">
         <v>-3930900</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="3">
         <v>2160400</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD100" s="3">
         <v>178600</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF100" s="3">
         <v>2184600</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-900200</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-2473800</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL100" s="3">
         <v>-953700</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-3721600</v>
       </c>
-      <c r="AN100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP100" s="3">
         <v>2384000</v>
       </c>
-      <c r="AP100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,68 +11096,68 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3">
         <v>2607300</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3">
         <v>2335200</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-2589300</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD101" s="3">
         <v>778700</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF101" s="3">
         <v>845800</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH101" s="3">
         <v>947500</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>1513000</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>0</v>
+      <c r="AK101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL101" s="3">
         <v>0</v>
@@ -10926,8 +11174,11 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -10970,82 +11221,85 @@
       <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>35686900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3">
         <v>9436000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z102" s="3">
         <v>73274000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD102" s="3">
         <v>4652100</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="3">
         <v>3339800</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH102" s="3">
         <v>14449100</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-32755500</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="3">
         <v>3766500</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="3">
         <v>16455100</v>
       </c>
-      <c r="AN102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP102" s="3">
         <v>-14530600</v>
       </c>
-      <c r="AP102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
